--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVII/LTAIPT_A63F37A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVII/LTAIPT_A63F37A.xlsx
@@ -12,18 +12,20 @@
     <sheet name="Hidden_1_Tabla_436804" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_2_Tabla_436804" sheetId="4" r:id="rId4"/>
     <sheet name="Hidden_3_Tabla_436804" sheetId="5" r:id="rId5"/>
+    <sheet name="Hidden_4_Tabla_436804" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="Hidden_1_Tabla_4368047">Hidden_1_Tabla_436804!$A$1:$A$26</definedName>
-    <definedName name="Hidden_2_Tabla_43680411">Hidden_2_Tabla_436804!$A$1:$A$41</definedName>
-    <definedName name="Hidden_3_Tabla_43680418">Hidden_3_Tabla_436804!$A$1:$A$32</definedName>
+    <definedName name="Hidden_1_Tabla_4368046">Hidden_1_Tabla_436804!$A$1:$A$2</definedName>
+    <definedName name="Hidden_2_Tabla_4368048">Hidden_2_Tabla_436804!$A$1:$A$26</definedName>
+    <definedName name="Hidden_3_Tabla_43680412">Hidden_3_Tabla_436804!$A$1:$A$41</definedName>
+    <definedName name="Hidden_4_Tabla_43680419">Hidden_4_Tabla_436804!$A$1:$A$32</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="218">
   <si>
     <t>49001</t>
   </si>
@@ -182,16 +184,16 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>CE86E159569492B156C7EC855673636C</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>4B0B5091D6D3E95BDB062646754F5559</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t>Ver nota</t>
@@ -200,22 +202,13 @@
     <t/>
   </si>
   <si>
-    <t>4702919</t>
-  </si>
-  <si>
-    <t>03/01/2023</t>
-  </si>
-  <si>
-    <t>Del periodo 01/10/2022 al 31/12/2022 en esta Subdirección de Actividades Paraescolares se encuentra impedida para reportar los mecanismos de participación ciudadana consagradas en el artículo XXXVII, toda vez que dentro del objeto del organismo público desconcentrado, Colegio de Bachilleres del estado de Tlaxcala no se encuentra dentro de su objeto desarrollar este tipo de actividades.</t>
-  </si>
-  <si>
-    <t>4330034</t>
-  </si>
-  <si>
-    <t>2799613</t>
-  </si>
-  <si>
-    <t>2255141</t>
+    <t>6230087</t>
+  </si>
+  <si>
+    <t>18/04/2023</t>
+  </si>
+  <si>
+    <t>Del periodo 01/01/2023 al 31/03/2023 en esta Subdirección de Actividades Paraescolares se encuentra impedida para reportar los mecanismos de participación ciudadana consagradas en el artículo XXXVII, toda vez que dentro del objeto del organismo público desconcentrado, Colegio de Bachilleres del estado de Tlaxcala no se encuentra dentro de su objeto desarrollar este tipo de actividades.</t>
   </si>
   <si>
     <t>9</t>
@@ -233,6 +226,9 @@
     <t>56509</t>
   </si>
   <si>
+    <t>77795</t>
+  </si>
+  <si>
     <t>56510</t>
   </si>
   <si>
@@ -290,13 +286,16 @@
     <t xml:space="preserve">Nombre del(as) área(s) que gestiona el mecanismo de participación </t>
   </si>
   <si>
-    <t>Nombre(s) del Servidor Público de contacto</t>
-  </si>
-  <si>
-    <t>Primer apellido del servidor público de contacto</t>
-  </si>
-  <si>
-    <t>Segundo apellido del servidor público de contacto</t>
+    <t>Nombre(s) del/la Servidor(a) Público(a) de contacto</t>
+  </si>
+  <si>
+    <t>Primer apellido del/la servidor(a) público(a) de contacto</t>
+  </si>
+  <si>
+    <t>Segundo apellido del/la servidor(a) público(a) de contacto</t>
+  </si>
+  <si>
+    <t>Sexo (catálogo)</t>
   </si>
   <si>
     <t>Correo electrónico oficial</t>
@@ -350,13 +349,13 @@
     <t>Horario y días de atención</t>
   </si>
   <si>
-    <t>B205458BC53BF25B8F229EE6014D65F8</t>
+    <t>BD0B4EC0657B56EA8709C2DC1A9802E1</t>
   </si>
   <si>
     <t>Subdirección de Actividades Paraescolares</t>
   </si>
   <si>
-    <t>Alejandro Herrera</t>
+    <t>Alejandro Alonso</t>
   </si>
   <si>
     <t>Herrera</t>
@@ -365,7 +364,7 @@
     <t>Lumbreras</t>
   </si>
   <si>
-    <t>sub.paraescolares@cobatlaxcale .edu.mx</t>
+    <t>sub.paraescolares@cobatlaxcala.edu.mx</t>
   </si>
   <si>
     <t>Miguel N. Lira</t>
@@ -386,31 +385,16 @@
     <t>90000</t>
   </si>
   <si>
-    <t>2464620026</t>
-  </si>
-  <si>
-    <t>Lunes y Viernes 8:00 a 17:30</t>
-  </si>
-  <si>
-    <t>5D54142CE5B00C01BE9ABC25A0F962F9</t>
-  </si>
-  <si>
-    <t>592AE9017C425F82BB599344B388CFEE</t>
-  </si>
-  <si>
-    <t>Alejandro Alonso</t>
-  </si>
-  <si>
-    <t>sub.paraescolares@cobatlaxcala.edu.mx</t>
-  </si>
-  <si>
     <t>4620026</t>
   </si>
   <si>
     <t>Lunes a Viernes 8:30 a 175:30</t>
   </si>
   <si>
-    <t>9642B28B6E85609A1B8CFA78E1947670</t>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
   <si>
     <t>Carretera</t>
@@ -1094,7 +1078,7 @@
   <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -1432,35 +1416,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="72.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="51" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="53.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="43.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="35" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="40.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="35" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="28.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>8</v>
       </c>
@@ -1474,46 +1459,46 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
-        <v>64</v>
-      </c>
       <c r="I1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>6</v>
       </c>
       <c r="K1" t="s">
         <v>6</v>
       </c>
       <c r="L1" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="M1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>6</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>8</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>8</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>6</v>
       </c>
-      <c r="S1" t="s">
-        <v>64</v>
-      </c>
       <c r="T1" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="U1" t="s">
         <v>6</v>
@@ -1522,194 +1507,203 @@
         <v>6</v>
       </c>
       <c r="W1" t="s">
+        <v>6</v>
+      </c>
+      <c r="X1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
         <v>65</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>66</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>67</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>68</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>69</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>70</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>71</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>72</v>
       </c>
-      <c r="K2" t="s">
+      <c r="N2" t="s">
         <v>73</v>
       </c>
-      <c r="L2" t="s">
+      <c r="O2" t="s">
         <v>74</v>
       </c>
-      <c r="M2" t="s">
+      <c r="P2" t="s">
         <v>75</v>
       </c>
-      <c r="N2" t="s">
+      <c r="Q2" t="s">
         <v>76</v>
       </c>
-      <c r="O2" t="s">
+      <c r="R2" t="s">
         <v>77</v>
       </c>
-      <c r="P2" t="s">
+      <c r="S2" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="T2" t="s">
         <v>79</v>
       </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>80</v>
       </c>
-      <c r="S2" t="s">
+      <c r="V2" t="s">
         <v>81</v>
       </c>
-      <c r="T2" t="s">
+      <c r="W2" t="s">
         <v>82</v>
       </c>
-      <c r="U2" t="s">
+      <c r="X2" t="s">
         <v>83</v>
       </c>
-      <c r="V2" t="s">
+    </row>
+    <row r="3" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="W2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="W3" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:24" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="I4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>117</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>57</v>
@@ -1718,241 +1712,34 @@
         <v>57</v>
       </c>
       <c r="T4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="W4" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="U4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="V4" s="3" t="s">
+      <c r="X4" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="W4" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="W6" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>127</v>
-      </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H201">
-      <formula1>Hidden_1_Tabla_4368047</formula1>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G4:G201">
+      <formula1>Hidden_1_Tabla_4368046</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L4:L201">
-      <formula1>Hidden_2_Tabla_43680411</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I201">
+      <formula1>Hidden_2_Tabla_4368048</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="S4:S201">
-      <formula1>Hidden_3_Tabla_43680418</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M4:M201">
+      <formula1>Hidden_3_Tabla_43680412</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T4:T201">
+      <formula1>Hidden_4_Tabla_43680419</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1961,137 +1748,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2101,212 +1768,137 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>192</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2316,167 +1908,382 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
